--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/PbcInitProdRaisingSub.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/PbcInitProdRaisingSub.xlsx
@@ -1,22 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9302"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="18420" windowHeight="5860"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
   </bookViews>
   <sheets>
     <sheet name="产品起始募集信息" sheetId="5" r:id="rId1"/>
     <sheet name="填写说明" sheetId="4" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
-  <oleSize ref="A1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="193">
   <si>
     <t>币种</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -604,14 +603,6 @@
   </si>
   <si>
     <t>反馈产品代码</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>内部产品代码</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>产品起始日</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -736,7 +727,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -778,7 +769,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -813,7 +804,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1022,19 +1013,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P1"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:N1"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="6" width="9" style="4"/>
-    <col min="7" max="7" width="11.90625" style="4" customWidth="1"/>
-    <col min="8" max="10" width="13" style="4" customWidth="1"/>
-    <col min="11" max="13" width="9" style="4"/>
+    <col min="7" max="7" width="11.875" style="4" customWidth="1"/>
+    <col min="8" max="8" width="13" style="4" customWidth="1"/>
+    <col min="9" max="11" width="9" style="4"/>
+    <col min="12" max="12" width="13" style="4" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="21.375" style="4" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="13" style="4" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="21.36328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13" style="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A1" s="5" t="s">
         <v>179</v>
       </c>
@@ -1060,27 +1051,21 @@
         <v>192</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="M1" s="5" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="N1" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="O1" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="P1" s="5" t="s">
         <v>191</v>
       </c>
     </row>
@@ -1094,903 +1079,903 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:A179"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="31.90625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="31.875" style="2" customWidth="1"/>
     <col min="2" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A2" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A3" s="3" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A4" s="3" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A5" s="3" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A6" s="3" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A7" s="3" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A8" s="3" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A9" s="3" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A10" s="3" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A11" s="3" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A12" s="3" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A13" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A14" s="3" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A15" s="3" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A16" s="3" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A17" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A18" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A19" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A20" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A21" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A22" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A23" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A24" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A25" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A26" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A27" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A28" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="29" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A29" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="30" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A30" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="31" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A31" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="32" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A32" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="33" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A33" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="34" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A34" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="35" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A35" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="36" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A36" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="37" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A37" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="38" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A38" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="39" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A39" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="40" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A40" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="41" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A41" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="42" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A42" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="43" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A43" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="44" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A44" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="45" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A45" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="46" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A46" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="47" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A47" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="48" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A48" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="49" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A49" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="50" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A50" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="51" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A51" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="52" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A52" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="53" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A53" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="54" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A54" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="55" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A55" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="56" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A56" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="57" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A57" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="58" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A58" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="59" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A59" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="60" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A60" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="61" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A61" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="62" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A62" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="63" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A63" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="64" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A64" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="65" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A65" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="66" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A66" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="67" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A67" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="68" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A68" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="69" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A69" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="70" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A70" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="71" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A71" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="72" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A72" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="73" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A73" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="74" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A74" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="75" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A75" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="76" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A76" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="77" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A77" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="78" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A78" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="79" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A79" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="80" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A80" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="81" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A81" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="82" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A82" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="83" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A83" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="84" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A84" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="85" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A85" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="86" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A86" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="87" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A87" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="88" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A88" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="89" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A89" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="90" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A90" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="91" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A91" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="92" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A92" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="93" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A93" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="94" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A94" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="95" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A95" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="96" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A96" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="97" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A97" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="98" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="98" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A98" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="99" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="99" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A99" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="100" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A100" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="101" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A101" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="102" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A102" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="103" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A103" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="104" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="104" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A104" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="105" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="105" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A105" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="106" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="106" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A106" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="107" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="107" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A107" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="108" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="108" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A108" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="109" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="109" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A109" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="110" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="110" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A110" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="111" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="111" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A111" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="112" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="112" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A112" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="113" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A113" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="114" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A114" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="115" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="115" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A115" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="116" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="116" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A116" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="117" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="117" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A117" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="118" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="118" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A118" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="119" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A119" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="120" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="120" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A120" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="121" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="121" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A121" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="122" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="122" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A122" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="123" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="123" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A123" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="124" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="124" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A124" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="125" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="125" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A125" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="126" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="126" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A126" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="127" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="127" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A127" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="128" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="128" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A128" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="129" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="129" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A129" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="130" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="130" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A130" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="131" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="131" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A131" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="132" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="132" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A132" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="133" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="133" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A133" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="134" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="134" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A134" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="135" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="135" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A135" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="136" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="136" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A136" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="137" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="137" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A137" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="138" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="138" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A138" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="139" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="139" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A139" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="140" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="140" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A140" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="141" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="141" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A141" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="142" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="142" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A142" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="143" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="143" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A143" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="144" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="144" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A144" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="145" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="145" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A145" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="146" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="146" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A146" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="147" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="147" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A147" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="148" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="148" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A148" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="149" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="149" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A149" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="150" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="150" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A150" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="151" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="151" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A151" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="152" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="152" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A152" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="153" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="153" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A153" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="154" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="154" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A154" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="155" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="155" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A155" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="156" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="156" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A156" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="157" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="157" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A157" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="158" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="158" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A158" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="159" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="159" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A159" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="160" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="160" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A160" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="161" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="161" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A161" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="162" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="162" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A162" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="163" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="163" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A163" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="164" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="164" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A164" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="165" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="165" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A165" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="166" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="166" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A166" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="167" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="167" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A167" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="168" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="168" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A168" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="169" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="169" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A169" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="170" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="170" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A170" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="171" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="171" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A171" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="172" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="172" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A172" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="173" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="173" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A173" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="174" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="174" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A174" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="175" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="175" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A175" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="176" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="176" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A176" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="177" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="177" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A177" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="178" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="178" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A178" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="179" spans="1:1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="179" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A179" t="s">
         <v>176</v>
       </c>

--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/PbcInitProdRaisingSub.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/PbcInitProdRaisingSub.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="240" yWindow="110" windowWidth="14810" windowHeight="8010"/>
   </bookViews>
   <sheets>
     <sheet name="产品起始募集信息" sheetId="5" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="195">
   <si>
     <t>币种</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -556,72 +556,80 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>报送日期</t>
+  </si>
+  <si>
+    <t>反馈状态</t>
+  </si>
+  <si>
+    <t>产品代码</t>
+  </si>
+  <si>
+    <t>地区</t>
+  </si>
+  <si>
+    <t>客户类型</t>
+  </si>
+  <si>
+    <t>起始募集金额</t>
+  </si>
+  <si>
+    <t>内部产品代码</t>
+  </si>
+  <si>
+    <t>产品起始日期</t>
+  </si>
+  <si>
     <t>数据状态</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>数据日期</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>报送状态</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>报送日期</t>
   </si>
   <si>
     <t>报送截止日</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>反馈状态</t>
-  </si>
-  <si>
-    <t>产品代码</t>
-  </si>
-  <si>
-    <t>地区</t>
-  </si>
-  <si>
-    <t>客户类型</t>
+  </si>
+  <si>
+    <t>反馈产品代码</t>
   </si>
   <si>
     <t>币种</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>起始募集金额</t>
   </si>
   <si>
     <t>起始募集金额折人民币</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>起始募集份额</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>反馈产品代码</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
-      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -630,15 +638,6 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -646,8 +645,14 @@
       <sz val="11"/>
       <color rgb="FF373737"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -688,33 +693,32 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="常规 2" xfId="1"/>
+    <cellStyle name="常规 3" xfId="2"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
-  <colors>
-    <mruColors>
-      <color rgb="FF00CCFF"/>
-      <color rgb="FF3399FF"/>
-    </mruColors>
-  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -727,7 +731,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -769,7 +773,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -804,7 +808,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1013,60 +1017,66 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N1"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:P1"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="6" width="9" style="4"/>
-    <col min="7" max="7" width="11.875" style="4" customWidth="1"/>
-    <col min="8" max="8" width="13" style="4" customWidth="1"/>
-    <col min="9" max="11" width="9" style="4"/>
-    <col min="12" max="12" width="13" style="4" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="21.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="6" width="9" style="4" customWidth="1"/>
+    <col min="7" max="7" width="12.6328125" style="4" customWidth="1"/>
+    <col min="8" max="10" width="12.36328125" style="4" customWidth="1"/>
+    <col min="11" max="13" width="9" style="4" customWidth="1"/>
     <col min="14" max="14" width="13" style="4" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="21.36328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13" style="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:16" s="5" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="D1" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="E1" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="F1" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="G1" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="H1" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="K1" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="L1" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="M1" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="N1" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="G1" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="K1" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="L1" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="M1" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="N1" s="5" t="s">
-        <v>191</v>
+      <c r="O1" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="P1" s="6" t="s">
+        <v>194</v>
       </c>
     </row>
   </sheetData>
@@ -1079,903 +1089,903 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:A179"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="31.875" style="2" customWidth="1"/>
+    <col min="1" max="1" width="31.90625" style="2" customWidth="1"/>
     <col min="2" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="128" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="129" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="130" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="131" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="132" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="133" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="134" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="134" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="135" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="135" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="136" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="136" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="137" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="137" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="138" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="138" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="139" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="139" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="140" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="140" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="141" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="141" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="142" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="142" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="143" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="143" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="144" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="144" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="145" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="146" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="146" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="147" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="147" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="148" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="148" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="149" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="149" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="150" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="150" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="151" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="151" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="152" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="152" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="153" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="153" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="154" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="154" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="155" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="155" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="156" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="156" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="157" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="157" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="158" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="158" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="159" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="159" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="160" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="160" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="161" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="161" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="162" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="162" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="163" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="163" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="164" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="164" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="165" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="165" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="166" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="166" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="167" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="167" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="168" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="168" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="169" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="169" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="170" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="170" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="171" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="171" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="172" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="172" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="173" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="173" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="174" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="174" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="175" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="175" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="176" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="176" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="177" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="177" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="178" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="178" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="179" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="179" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>176</v>
       </c>
